--- a/pyt_front/public/templates/pyt/baseball/pyt_seller_upload_only_template.xlsx
+++ b/pyt_front/public/templates/pyt/baseball/pyt_seller_upload_only_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1차" sheetId="1" r:id="R8d718fdbad7d4a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차" sheetId="2" r:id="Rfe91f2b928974999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1차" sheetId="1" r:id="R6eaa6d38a87b45ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2차" sheetId="2" r:id="Reba4b472ed8143ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -83,7 +83,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -115,231 +115,61 @@
         <x:fgColor rgb="FF2563EB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2563EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="38">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="170">
+  <x:cellXfs count="175">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -733,6 +563,15 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -784,9 +623,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -893,9 +732,9 @@
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -922,14 +761,15 @@
       </x:c>
       <x:c r="B3" s="113" t="str"/>
       <x:c r="C3" s="114"/>
-      <x:c r="D3" s="115" t="str">
+      <x:c r="D3"/>
+      <x:c r="E3" s="116" t="str">
+        <x:f>"팀 가격 합계"</x:f>
         <x:v>팀 가격 합계</x:v>
       </x:c>
-      <x:c r="E3" s="116" t="n">
+      <x:c r="F3" s="111" t="n">
         <x:f>SUM(C12:C41)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F3" s="111"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="117" t="str">
@@ -937,14 +777,15 @@
       </x:c>
       <x:c r="B4" s="118" t="str"/>
       <x:c r="C4" s="119"/>
-      <x:c r="D4" s="120" t="str">
+      <x:c r="D4"/>
+      <x:c r="E4" s="121" t="str">
+        <x:f>"차액"</x:f>
         <x:v>차액</x:v>
       </x:c>
-      <x:c r="E4" s="121" t="n">
-        <x:f>B8-E3</x:f>
+      <x:c r="F4" s="111" t="n">
+        <x:f>B8-F3</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F4" s="111"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="117" t="str">
@@ -954,14 +795,15 @@
         <x:v>한케이스</x:v>
       </x:c>
       <x:c r="C5" s="119"/>
-      <x:c r="D5" s="120" t="str">
+      <x:c r="D5"/>
+      <x:c r="E5" s="122" t="str">
+        <x:f>"등록 체크"</x:f>
         <x:v>등록 체크</x:v>
       </x:c>
-      <x:c r="E5" s="122" t="str">
-        <x:f>IF(E4=0,"등록 가능","금액 확인")</x:f>
+      <x:c r="F5" s="111" t="str">
+        <x:f>IF(F4=0,"등록 가능","금액 확인")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
-      <x:c r="F5" s="111"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="117" t="str">
@@ -969,13 +811,15 @@
       </x:c>
       <x:c r="B6" s="118" t="str"/>
       <x:c r="C6" s="119"/>
-      <x:c r="D6" s="123" t="str">
+      <x:c r="D6"/>
+      <x:c r="E6" s="124" t="str">
+        <x:f>"입력 기준"</x:f>
         <x:v>입력 기준</x:v>
       </x:c>
-      <x:c r="E6" s="124" t="str">
+      <x:c r="F6" s="111" t="str">
+        <x:f>"노란색 칸만 입력"</x:f>
         <x:v>노란색 칸만 입력</x:v>
       </x:c>
-      <x:c r="F6" s="111"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="117" t="str">
@@ -985,7 +829,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="119"/>
-      <x:c r="D7" s="119"/>
+      <x:c r="D7"/>
       <x:c r="E7" s="125"/>
       <x:c r="F7" s="111"/>
     </x:row>
@@ -995,7 +839,7 @@
       </x:c>
       <x:c r="B8" s="127" t="str"/>
       <x:c r="C8" s="128"/>
-      <x:c r="D8" s="128"/>
+      <x:c r="D8"/>
       <x:c r="E8" s="129"/>
       <x:c r="F8" s="111"/>
     </x:row>
@@ -1025,7 +869,9 @@
       <x:c r="C11" s="130" t="str">
         <x:v>판매가</x:v>
       </x:c>
-      <x:c r="D11" s="111"/>
+      <x:c r="D11" s="172" t="str">
+        <x:v>필러 전용</x:v>
+      </x:c>
       <x:c r="E11" s="111"/>
       <x:c r="F11" s="111"/>
     </x:row>
@@ -1037,7 +883,7 @@
         <x:v>Arizona Diamondbacks</x:v>
       </x:c>
       <x:c r="C12" s="133" t="str"/>
-      <x:c r="D12" s="111"/>
+      <x:c r="D12" s="174"/>
       <x:c r="E12" s="111"/>
       <x:c r="F12" s="111"/>
     </x:row>
@@ -1049,7 +895,7 @@
         <x:v>Atlanta Braves</x:v>
       </x:c>
       <x:c r="C13" s="136" t="str"/>
-      <x:c r="D13" s="111"/>
+      <x:c r="D13" s="174"/>
       <x:c r="E13" s="111"/>
       <x:c r="F13" s="111"/>
     </x:row>
@@ -1061,7 +907,7 @@
         <x:v>Baltimore Orioles</x:v>
       </x:c>
       <x:c r="C14" s="136" t="str"/>
-      <x:c r="D14" s="111"/>
+      <x:c r="D14" s="174"/>
       <x:c r="E14" s="111"/>
       <x:c r="F14" s="111"/>
     </x:row>
@@ -1073,7 +919,7 @@
         <x:v>Boston Red Sox</x:v>
       </x:c>
       <x:c r="C15" s="136" t="str"/>
-      <x:c r="D15" s="111"/>
+      <x:c r="D15" s="174"/>
       <x:c r="E15" s="111"/>
       <x:c r="F15" s="111"/>
     </x:row>
@@ -1085,7 +931,7 @@
         <x:v>Chicago Cubs</x:v>
       </x:c>
       <x:c r="C16" s="136" t="str"/>
-      <x:c r="D16" s="111"/>
+      <x:c r="D16" s="174"/>
       <x:c r="E16" s="111"/>
       <x:c r="F16" s="111"/>
     </x:row>
@@ -1097,7 +943,7 @@
         <x:v>Chicago White Sox</x:v>
       </x:c>
       <x:c r="C17" s="136" t="str"/>
-      <x:c r="D17" s="111"/>
+      <x:c r="D17" s="174"/>
       <x:c r="E17" s="111"/>
       <x:c r="F17" s="111"/>
     </x:row>
@@ -1109,7 +955,7 @@
         <x:v>Cincinnati Reds</x:v>
       </x:c>
       <x:c r="C18" s="136" t="str"/>
-      <x:c r="D18" s="111"/>
+      <x:c r="D18" s="174"/>
       <x:c r="E18" s="111"/>
       <x:c r="F18" s="111"/>
     </x:row>
@@ -1121,7 +967,7 @@
         <x:v>Cleveland Guardians</x:v>
       </x:c>
       <x:c r="C19" s="136" t="str"/>
-      <x:c r="D19" s="111"/>
+      <x:c r="D19" s="174"/>
       <x:c r="E19" s="111"/>
       <x:c r="F19" s="111"/>
     </x:row>
@@ -1133,7 +979,7 @@
         <x:v>Colorado Rockies</x:v>
       </x:c>
       <x:c r="C20" s="136" t="str"/>
-      <x:c r="D20" s="111"/>
+      <x:c r="D20" s="174"/>
       <x:c r="E20" s="111"/>
       <x:c r="F20" s="111"/>
     </x:row>
@@ -1145,7 +991,7 @@
         <x:v>Detroit Tigers</x:v>
       </x:c>
       <x:c r="C21" s="136" t="str"/>
-      <x:c r="D21" s="111"/>
+      <x:c r="D21" s="174"/>
       <x:c r="E21" s="111"/>
       <x:c r="F21" s="111"/>
     </x:row>
@@ -1157,7 +1003,7 @@
         <x:v>Houston Astros</x:v>
       </x:c>
       <x:c r="C22" s="136" t="str"/>
-      <x:c r="D22" s="111"/>
+      <x:c r="D22" s="174"/>
       <x:c r="E22" s="111"/>
       <x:c r="F22" s="111"/>
     </x:row>
@@ -1169,7 +1015,7 @@
         <x:v>Kansas City Royals</x:v>
       </x:c>
       <x:c r="C23" s="136" t="str"/>
-      <x:c r="D23" s="111"/>
+      <x:c r="D23" s="174"/>
       <x:c r="E23" s="111"/>
       <x:c r="F23" s="111"/>
     </x:row>
@@ -1181,7 +1027,7 @@
         <x:v>Los Angeles Angels</x:v>
       </x:c>
       <x:c r="C24" s="136" t="str"/>
-      <x:c r="D24" s="111"/>
+      <x:c r="D24" s="174"/>
       <x:c r="E24" s="111"/>
       <x:c r="F24" s="111"/>
     </x:row>
@@ -1193,7 +1039,7 @@
         <x:v>Los Angeles Dodgers</x:v>
       </x:c>
       <x:c r="C25" s="136" t="str"/>
-      <x:c r="D25" s="111"/>
+      <x:c r="D25" s="174"/>
       <x:c r="E25" s="111"/>
       <x:c r="F25" s="111"/>
     </x:row>
@@ -1205,7 +1051,7 @@
         <x:v>Miami Marlins</x:v>
       </x:c>
       <x:c r="C26" s="136" t="str"/>
-      <x:c r="D26" s="111"/>
+      <x:c r="D26" s="174"/>
       <x:c r="E26" s="111"/>
       <x:c r="F26" s="111"/>
     </x:row>
@@ -1217,7 +1063,7 @@
         <x:v>Milwaukee Brewers</x:v>
       </x:c>
       <x:c r="C27" s="136" t="str"/>
-      <x:c r="D27" s="111"/>
+      <x:c r="D27" s="174"/>
       <x:c r="E27" s="111"/>
       <x:c r="F27" s="111"/>
     </x:row>
@@ -1229,7 +1075,7 @@
         <x:v>Minnesota Twins</x:v>
       </x:c>
       <x:c r="C28" s="136" t="str"/>
-      <x:c r="D28" s="111"/>
+      <x:c r="D28" s="174"/>
       <x:c r="E28" s="111"/>
       <x:c r="F28" s="111"/>
     </x:row>
@@ -1241,7 +1087,7 @@
         <x:v>New York Mets</x:v>
       </x:c>
       <x:c r="C29" s="136" t="str"/>
-      <x:c r="D29" s="111"/>
+      <x:c r="D29" s="174"/>
       <x:c r="E29" s="111"/>
       <x:c r="F29" s="111"/>
     </x:row>
@@ -1253,7 +1099,7 @@
         <x:v>New York Yankees</x:v>
       </x:c>
       <x:c r="C30" s="136" t="str"/>
-      <x:c r="D30" s="111"/>
+      <x:c r="D30" s="174"/>
       <x:c r="E30" s="111"/>
       <x:c r="F30" s="111"/>
     </x:row>
@@ -1265,7 +1111,7 @@
         <x:v>Athletics</x:v>
       </x:c>
       <x:c r="C31" s="136" t="str"/>
-      <x:c r="D31" s="111"/>
+      <x:c r="D31" s="174"/>
       <x:c r="E31" s="111"/>
       <x:c r="F31" s="111"/>
     </x:row>
@@ -1277,7 +1123,7 @@
         <x:v>Philadelphia Phillies</x:v>
       </x:c>
       <x:c r="C32" s="136" t="str"/>
-      <x:c r="D32" s="111"/>
+      <x:c r="D32" s="174"/>
       <x:c r="E32" s="111"/>
       <x:c r="F32" s="111"/>
     </x:row>
@@ -1289,7 +1135,7 @@
         <x:v>Pittsburgh Pirates</x:v>
       </x:c>
       <x:c r="C33" s="136" t="str"/>
-      <x:c r="D33" s="111"/>
+      <x:c r="D33" s="174"/>
       <x:c r="E33" s="111"/>
       <x:c r="F33" s="111"/>
     </x:row>
@@ -1301,7 +1147,7 @@
         <x:v>San Diego Padres</x:v>
       </x:c>
       <x:c r="C34" s="136" t="str"/>
-      <x:c r="D34" s="111"/>
+      <x:c r="D34" s="174"/>
       <x:c r="E34" s="111"/>
       <x:c r="F34" s="111"/>
     </x:row>
@@ -1313,7 +1159,7 @@
         <x:v>San Francisco Giants</x:v>
       </x:c>
       <x:c r="C35" s="136" t="str"/>
-      <x:c r="D35" s="111"/>
+      <x:c r="D35" s="174"/>
       <x:c r="E35" s="111"/>
       <x:c r="F35" s="111"/>
     </x:row>
@@ -1325,7 +1171,7 @@
         <x:v>Seattle Mariners</x:v>
       </x:c>
       <x:c r="C36" s="136" t="str"/>
-      <x:c r="D36" s="111"/>
+      <x:c r="D36" s="174"/>
       <x:c r="E36" s="111"/>
       <x:c r="F36" s="111"/>
     </x:row>
@@ -1337,7 +1183,7 @@
         <x:v>St. Louis Cardinals</x:v>
       </x:c>
       <x:c r="C37" s="136" t="str"/>
-      <x:c r="D37" s="111"/>
+      <x:c r="D37" s="174"/>
       <x:c r="E37" s="111"/>
       <x:c r="F37" s="111"/>
     </x:row>
@@ -1349,7 +1195,7 @@
         <x:v>Tampa Bay Rays</x:v>
       </x:c>
       <x:c r="C38" s="136" t="str"/>
-      <x:c r="D38" s="111"/>
+      <x:c r="D38" s="174"/>
       <x:c r="E38" s="111"/>
       <x:c r="F38" s="111"/>
     </x:row>
@@ -1361,7 +1207,7 @@
         <x:v>Texas Rangers</x:v>
       </x:c>
       <x:c r="C39" s="136" t="str"/>
-      <x:c r="D39" s="111"/>
+      <x:c r="D39" s="174"/>
       <x:c r="E39" s="111"/>
       <x:c r="F39" s="111"/>
     </x:row>
@@ -1373,7 +1219,7 @@
         <x:v>Toronto Blue Jays</x:v>
       </x:c>
       <x:c r="C40" s="136" t="str"/>
-      <x:c r="D40" s="111"/>
+      <x:c r="D40" s="174"/>
       <x:c r="E40" s="111"/>
       <x:c r="F40" s="111"/>
     </x:row>
@@ -1385,7 +1231,7 @@
         <x:v>Washington Nationals</x:v>
       </x:c>
       <x:c r="C41" s="139" t="str"/>
-      <x:c r="D41" s="111"/>
+      <x:c r="D41" s="174"/>
       <x:c r="E41" s="111"/>
       <x:c r="F41" s="111"/>
     </x:row>
@@ -1441,9 +1287,9 @@
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -1470,14 +1316,15 @@
       </x:c>
       <x:c r="B3" s="113" t="str"/>
       <x:c r="C3" s="114"/>
-      <x:c r="D3" s="115" t="str">
+      <x:c r="D3"/>
+      <x:c r="E3" s="116" t="str">
+        <x:f>"팀 가격 합계"</x:f>
         <x:v>팀 가격 합계</x:v>
       </x:c>
-      <x:c r="E3" s="116" t="n">
+      <x:c r="F3" s="111" t="n">
         <x:f>SUM(C12:C41)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F3" s="111"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="117" t="str">
@@ -1485,14 +1332,15 @@
       </x:c>
       <x:c r="B4" s="118" t="str"/>
       <x:c r="C4" s="119"/>
-      <x:c r="D4" s="120" t="str">
+      <x:c r="D4"/>
+      <x:c r="E4" s="121" t="str">
+        <x:f>"차액"</x:f>
         <x:v>차액</x:v>
       </x:c>
-      <x:c r="E4" s="121" t="n">
-        <x:f>B8-E3</x:f>
+      <x:c r="F4" s="111" t="n">
+        <x:f>B8-F3</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F4" s="111"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="117" t="str">
@@ -1502,14 +1350,15 @@
         <x:v>한케이스</x:v>
       </x:c>
       <x:c r="C5" s="119"/>
-      <x:c r="D5" s="120" t="str">
+      <x:c r="D5"/>
+      <x:c r="E5" s="122" t="str">
+        <x:f>"등록 체크"</x:f>
         <x:v>등록 체크</x:v>
       </x:c>
-      <x:c r="E5" s="122" t="str">
-        <x:f>IF(E4=0,"등록 가능","금액 확인")</x:f>
+      <x:c r="F5" s="111" t="str">
+        <x:f>IF(F4=0,"등록 가능","금액 확인")</x:f>
         <x:v>등록 가능</x:v>
       </x:c>
-      <x:c r="F5" s="111"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="117" t="str">
@@ -1517,13 +1366,15 @@
       </x:c>
       <x:c r="B6" s="118" t="str"/>
       <x:c r="C6" s="119"/>
-      <x:c r="D6" s="123" t="str">
+      <x:c r="D6"/>
+      <x:c r="E6" s="124" t="str">
+        <x:f>"입력 기준"</x:f>
         <x:v>입력 기준</x:v>
       </x:c>
-      <x:c r="E6" s="124" t="str">
+      <x:c r="F6" s="111" t="str">
+        <x:f>"노란색 칸만 입력"</x:f>
         <x:v>노란색 칸만 입력</x:v>
       </x:c>
-      <x:c r="F6" s="111"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="117" t="str">
@@ -1533,7 +1384,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="119"/>
-      <x:c r="D7" s="119"/>
+      <x:c r="D7"/>
       <x:c r="E7" s="125"/>
       <x:c r="F7" s="111"/>
     </x:row>
@@ -1543,7 +1394,7 @@
       </x:c>
       <x:c r="B8" s="127" t="str"/>
       <x:c r="C8" s="128"/>
-      <x:c r="D8" s="128"/>
+      <x:c r="D8"/>
       <x:c r="E8" s="129"/>
       <x:c r="F8" s="111"/>
     </x:row>
@@ -1573,7 +1424,9 @@
       <x:c r="C11" s="130" t="str">
         <x:v>판매가</x:v>
       </x:c>
-      <x:c r="D11" s="111"/>
+      <x:c r="D11" s="172" t="str">
+        <x:v>필러 전용</x:v>
+      </x:c>
       <x:c r="E11" s="111"/>
       <x:c r="F11" s="111"/>
     </x:row>
@@ -1585,7 +1438,7 @@
         <x:v>Arizona Diamondbacks</x:v>
       </x:c>
       <x:c r="C12" s="133" t="str"/>
-      <x:c r="D12" s="111"/>
+      <x:c r="D12" s="174"/>
       <x:c r="E12" s="111"/>
       <x:c r="F12" s="111"/>
     </x:row>
@@ -1597,7 +1450,7 @@
         <x:v>Atlanta Braves</x:v>
       </x:c>
       <x:c r="C13" s="136" t="str"/>
-      <x:c r="D13" s="111"/>
+      <x:c r="D13" s="174"/>
       <x:c r="E13" s="111"/>
       <x:c r="F13" s="111"/>
     </x:row>
@@ -1609,7 +1462,7 @@
         <x:v>Baltimore Orioles</x:v>
       </x:c>
       <x:c r="C14" s="136" t="str"/>
-      <x:c r="D14" s="111"/>
+      <x:c r="D14" s="174"/>
       <x:c r="E14" s="111"/>
       <x:c r="F14" s="111"/>
     </x:row>
@@ -1621,7 +1474,7 @@
         <x:v>Boston Red Sox</x:v>
       </x:c>
       <x:c r="C15" s="136" t="str"/>
-      <x:c r="D15" s="111"/>
+      <x:c r="D15" s="174"/>
       <x:c r="E15" s="111"/>
       <x:c r="F15" s="111"/>
     </x:row>
@@ -1633,7 +1486,7 @@
         <x:v>Chicago Cubs</x:v>
       </x:c>
       <x:c r="C16" s="136" t="str"/>
-      <x:c r="D16" s="111"/>
+      <x:c r="D16" s="174"/>
       <x:c r="E16" s="111"/>
       <x:c r="F16" s="111"/>
     </x:row>
@@ -1645,7 +1498,7 @@
         <x:v>Chicago White Sox</x:v>
       </x:c>
       <x:c r="C17" s="136" t="str"/>
-      <x:c r="D17" s="111"/>
+      <x:c r="D17" s="174"/>
       <x:c r="E17" s="111"/>
       <x:c r="F17" s="111"/>
     </x:row>
@@ -1657,7 +1510,7 @@
         <x:v>Cincinnati Reds</x:v>
       </x:c>
       <x:c r="C18" s="136" t="str"/>
-      <x:c r="D18" s="111"/>
+      <x:c r="D18" s="174"/>
       <x:c r="E18" s="111"/>
       <x:c r="F18" s="111"/>
     </x:row>
@@ -1669,7 +1522,7 @@
         <x:v>Cleveland Guardians</x:v>
       </x:c>
       <x:c r="C19" s="136" t="str"/>
-      <x:c r="D19" s="111"/>
+      <x:c r="D19" s="174"/>
       <x:c r="E19" s="111"/>
       <x:c r="F19" s="111"/>
     </x:row>
@@ -1681,7 +1534,7 @@
         <x:v>Colorado Rockies</x:v>
       </x:c>
       <x:c r="C20" s="136" t="str"/>
-      <x:c r="D20" s="111"/>
+      <x:c r="D20" s="174"/>
       <x:c r="E20" s="111"/>
       <x:c r="F20" s="111"/>
     </x:row>
@@ -1693,7 +1546,7 @@
         <x:v>Detroit Tigers</x:v>
       </x:c>
       <x:c r="C21" s="136" t="str"/>
-      <x:c r="D21" s="111"/>
+      <x:c r="D21" s="174"/>
       <x:c r="E21" s="111"/>
       <x:c r="F21" s="111"/>
     </x:row>
@@ -1705,7 +1558,7 @@
         <x:v>Houston Astros</x:v>
       </x:c>
       <x:c r="C22" s="136" t="str"/>
-      <x:c r="D22" s="111"/>
+      <x:c r="D22" s="174"/>
       <x:c r="E22" s="111"/>
       <x:c r="F22" s="111"/>
     </x:row>
@@ -1717,7 +1570,7 @@
         <x:v>Kansas City Royals</x:v>
       </x:c>
       <x:c r="C23" s="136" t="str"/>
-      <x:c r="D23" s="111"/>
+      <x:c r="D23" s="174"/>
       <x:c r="E23" s="111"/>
       <x:c r="F23" s="111"/>
     </x:row>
@@ -1729,7 +1582,7 @@
         <x:v>Los Angeles Angels</x:v>
       </x:c>
       <x:c r="C24" s="136" t="str"/>
-      <x:c r="D24" s="111"/>
+      <x:c r="D24" s="174"/>
       <x:c r="E24" s="111"/>
       <x:c r="F24" s="111"/>
     </x:row>
@@ -1741,7 +1594,7 @@
         <x:v>Los Angeles Dodgers</x:v>
       </x:c>
       <x:c r="C25" s="136" t="str"/>
-      <x:c r="D25" s="111"/>
+      <x:c r="D25" s="174"/>
       <x:c r="E25" s="111"/>
       <x:c r="F25" s="111"/>
     </x:row>
@@ -1753,7 +1606,7 @@
         <x:v>Miami Marlins</x:v>
       </x:c>
       <x:c r="C26" s="136" t="str"/>
-      <x:c r="D26" s="111"/>
+      <x:c r="D26" s="174"/>
       <x:c r="E26" s="111"/>
       <x:c r="F26" s="111"/>
     </x:row>
@@ -1765,7 +1618,7 @@
         <x:v>Milwaukee Brewers</x:v>
       </x:c>
       <x:c r="C27" s="136" t="str"/>
-      <x:c r="D27" s="111"/>
+      <x:c r="D27" s="174"/>
       <x:c r="E27" s="111"/>
       <x:c r="F27" s="111"/>
     </x:row>
@@ -1777,7 +1630,7 @@
         <x:v>Minnesota Twins</x:v>
       </x:c>
       <x:c r="C28" s="136" t="str"/>
-      <x:c r="D28" s="111"/>
+      <x:c r="D28" s="174"/>
       <x:c r="E28" s="111"/>
       <x:c r="F28" s="111"/>
     </x:row>
@@ -1789,7 +1642,7 @@
         <x:v>New York Mets</x:v>
       </x:c>
       <x:c r="C29" s="136" t="str"/>
-      <x:c r="D29" s="111"/>
+      <x:c r="D29" s="174"/>
       <x:c r="E29" s="111"/>
       <x:c r="F29" s="111"/>
     </x:row>
@@ -1801,7 +1654,7 @@
         <x:v>New York Yankees</x:v>
       </x:c>
       <x:c r="C30" s="136" t="str"/>
-      <x:c r="D30" s="111"/>
+      <x:c r="D30" s="174"/>
       <x:c r="E30" s="111"/>
       <x:c r="F30" s="111"/>
     </x:row>
@@ -1813,7 +1666,7 @@
         <x:v>Athletics</x:v>
       </x:c>
       <x:c r="C31" s="136" t="str"/>
-      <x:c r="D31" s="111"/>
+      <x:c r="D31" s="174"/>
       <x:c r="E31" s="111"/>
       <x:c r="F31" s="111"/>
     </x:row>
@@ -1825,7 +1678,7 @@
         <x:v>Philadelphia Phillies</x:v>
       </x:c>
       <x:c r="C32" s="136" t="str"/>
-      <x:c r="D32" s="111"/>
+      <x:c r="D32" s="174"/>
       <x:c r="E32" s="111"/>
       <x:c r="F32" s="111"/>
     </x:row>
@@ -1837,7 +1690,7 @@
         <x:v>Pittsburgh Pirates</x:v>
       </x:c>
       <x:c r="C33" s="136" t="str"/>
-      <x:c r="D33" s="111"/>
+      <x:c r="D33" s="174"/>
       <x:c r="E33" s="111"/>
       <x:c r="F33" s="111"/>
     </x:row>
@@ -1849,7 +1702,7 @@
         <x:v>San Diego Padres</x:v>
       </x:c>
       <x:c r="C34" s="136" t="str"/>
-      <x:c r="D34" s="111"/>
+      <x:c r="D34" s="174"/>
       <x:c r="E34" s="111"/>
       <x:c r="F34" s="111"/>
     </x:row>
@@ -1861,7 +1714,7 @@
         <x:v>San Francisco Giants</x:v>
       </x:c>
       <x:c r="C35" s="136" t="str"/>
-      <x:c r="D35" s="111"/>
+      <x:c r="D35" s="174"/>
       <x:c r="E35" s="111"/>
       <x:c r="F35" s="111"/>
     </x:row>
@@ -1873,7 +1726,7 @@
         <x:v>Seattle Mariners</x:v>
       </x:c>
       <x:c r="C36" s="136" t="str"/>
-      <x:c r="D36" s="111"/>
+      <x:c r="D36" s="174"/>
       <x:c r="E36" s="111"/>
       <x:c r="F36" s="111"/>
     </x:row>
@@ -1885,7 +1738,7 @@
         <x:v>St. Louis Cardinals</x:v>
       </x:c>
       <x:c r="C37" s="136" t="str"/>
-      <x:c r="D37" s="111"/>
+      <x:c r="D37" s="174"/>
       <x:c r="E37" s="111"/>
       <x:c r="F37" s="111"/>
     </x:row>
@@ -1897,7 +1750,7 @@
         <x:v>Tampa Bay Rays</x:v>
       </x:c>
       <x:c r="C38" s="136" t="str"/>
-      <x:c r="D38" s="111"/>
+      <x:c r="D38" s="174"/>
       <x:c r="E38" s="111"/>
       <x:c r="F38" s="111"/>
     </x:row>
@@ -1909,7 +1762,7 @@
         <x:v>Texas Rangers</x:v>
       </x:c>
       <x:c r="C39" s="136" t="str"/>
-      <x:c r="D39" s="111"/>
+      <x:c r="D39" s="174"/>
       <x:c r="E39" s="111"/>
       <x:c r="F39" s="111"/>
     </x:row>
@@ -1921,7 +1774,7 @@
         <x:v>Toronto Blue Jays</x:v>
       </x:c>
       <x:c r="C40" s="136" t="str"/>
-      <x:c r="D40" s="111"/>
+      <x:c r="D40" s="174"/>
       <x:c r="E40" s="111"/>
       <x:c r="F40" s="111"/>
     </x:row>
@@ -1933,7 +1786,7 @@
         <x:v>Washington Nationals</x:v>
       </x:c>
       <x:c r="C41" s="139" t="str"/>
-      <x:c r="D41" s="111"/>
+      <x:c r="D41" s="174"/>
       <x:c r="E41" s="111"/>
       <x:c r="F41" s="111"/>
     </x:row>
